--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:18</t>
+    <t xml:space="preserve">2026-09-09 23:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:13</t>
+    <t xml:space="preserve">2026-09-17 14:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:09</t>
+    <t xml:space="preserve">2026-09-23 12:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:38</t>
+    <t xml:space="preserve">2026-10-02 14:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_nuble.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Ñiquén</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">Yungay</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:51</t>
+    <t xml:space="preserve">2026-10-04 09:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:06</t>
+    <t xml:space="preserve">2026-10-05 11:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
